--- a/data_ankom/metadata.xlsx
+++ b/data_ankom/metadata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1YwZrMr_Yu2U7r-aXJu3Qa-LpH5rWwSG-\ARLAN ARAUJO RODRIGUES\3_INTELLECTUAL PRODUCTS\Rebecca Smith Lab\Jane Wernow\Stats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arlan\Desktop\rumenGP\data_ankom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8EA78B-B942-4FFF-AF56-0D59354BB10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D542F273-DFA6-4CC6-B3BD-9E5EF51EC7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{13B5C980-F356-944D-8F6C-78B1F36B7411}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="48 hr Incubation" sheetId="2" r:id="rId2"/>
     <sheet name="metadata" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -139,55 +139,28 @@
     <t>x</t>
   </si>
   <si>
-    <t>Weight_g</t>
-  </si>
-  <si>
     <t>Rep</t>
   </si>
   <si>
     <t>TMR</t>
   </si>
   <si>
-    <t>Sample1</t>
-  </si>
-  <si>
-    <t>Rep1</t>
-  </si>
-  <si>
-    <t>LH244</t>
-  </si>
-  <si>
-    <t>R123-5</t>
-  </si>
-  <si>
-    <t>R126-1</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
+    <t>LH244_2</t>
+  </si>
+  <si>
+    <t>LH244_5</t>
+  </si>
+  <si>
+    <t>R123_5_1</t>
+  </si>
+  <si>
+    <t>R123_5_5</t>
+  </si>
+  <si>
+    <t>R126_1_2</t>
+  </si>
+  <si>
+    <t>R126_1_3</t>
   </si>
 </sst>
 </file>
@@ -1965,808 +1938,513 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD47E061-5D39-4811-B47A-D9F9D6DB42BE}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="2"/>
-    <col min="2" max="3" width="11" style="2" customWidth="1"/>
+    <col min="1" max="3" width="10.875" style="2"/>
     <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="2" customWidth="1"/>
-    <col min="6" max="8" width="10.875" style="2"/>
-    <col min="9" max="9" width="11" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.5" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="10.875" style="2"/>
+    <col min="5" max="5" width="11" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="10.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>41</v>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
-        <v>1.0059</v>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2">
         <v>6.24</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
-      <c r="E3" s="2">
-        <v>1.0023</v>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2">
         <v>6.22</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>41</v>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
-      <c r="E4" s="2">
-        <v>1.0036</v>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F4" s="2">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2">
         <v>6.24</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
+      <c r="B5" s="2">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.0035000000000001</v>
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F5" s="2">
-        <v>4</v>
-      </c>
-      <c r="G5" s="2">
-        <v>4</v>
-      </c>
-      <c r="H5" s="2">
         <v>6.3</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>42</v>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1.0297000000000001</v>
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F6" s="2">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2">
         <v>6.15</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
+      <c r="B7" s="2">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>6</v>
       </c>
       <c r="D7" s="2">
-        <v>6</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1.0525</v>
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F7" s="2">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2">
-        <v>6</v>
-      </c>
-      <c r="H7" s="2">
         <v>6.16</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>43</v>
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>7</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="2">
-        <v>1.0405</v>
+      <c r="E8" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F8" s="2">
-        <v>7</v>
-      </c>
-      <c r="G8" s="2">
-        <v>7</v>
-      </c>
-      <c r="H8" s="2">
         <v>6.13</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
+      <c r="B9" s="2">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2">
+        <v>8</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" s="2">
-        <v>1.0781000000000001</v>
+      <c r="E9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="2">
-        <v>8</v>
-      </c>
-      <c r="H9" s="2">
         <v>6.12</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
+      <c r="B10" s="2">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2">
+        <v>9</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
       </c>
-      <c r="E10" s="2">
-        <v>1.0291999999999999</v>
+      <c r="E10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F10" s="2">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2">
         <v>6.12</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>44</v>
+      <c r="B11" s="2">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>10</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1.0509999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="F11" s="2">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2">
-        <v>10</v>
-      </c>
-      <c r="H11" s="2">
         <v>6.26</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>44</v>
+      <c r="B12" s="2">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2">
+        <v>11</v>
       </c>
       <c r="D12" s="2">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1.0105</v>
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="F12" s="2">
-        <v>11</v>
-      </c>
-      <c r="G12" s="2">
-        <v>11</v>
-      </c>
-      <c r="H12" s="2">
         <v>6.12</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>44</v>
+      <c r="B13" s="2">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2">
+        <v>12</v>
       </c>
       <c r="D13" s="2">
-        <v>6</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1.0359</v>
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="F13" s="2">
-        <v>12</v>
-      </c>
-      <c r="G13" s="2">
-        <v>12</v>
-      </c>
-      <c r="H13" s="2">
         <v>6.17</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>45</v>
+      <c r="B14" s="2">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2">
+        <v>13</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="2">
-        <v>1.014</v>
+      <c r="E14" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F14" s="2">
-        <v>13</v>
-      </c>
-      <c r="G14" s="2">
-        <v>13</v>
-      </c>
-      <c r="H14" s="2">
         <v>6.15</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>45</v>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2">
+        <v>14</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
-      <c r="E15" s="2">
-        <v>1.0044999999999999</v>
+      <c r="E15" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F15" s="2">
-        <v>14</v>
-      </c>
-      <c r="G15" s="2">
-        <v>14</v>
-      </c>
-      <c r="H15" s="2">
         <v>6.17</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>45</v>
+      <c r="B16" s="2">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2">
+        <v>15</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
       </c>
-      <c r="E16" s="2">
-        <v>1.0446</v>
+      <c r="E16" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F16" s="2">
-        <v>15</v>
-      </c>
-      <c r="G16" s="2">
-        <v>15</v>
-      </c>
-      <c r="H16" s="2">
         <v>6.12</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="2">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1.0454000000000001</v>
-      </c>
       <c r="F17" s="2">
-        <v>16</v>
-      </c>
-      <c r="G17" s="2">
-        <v>16</v>
-      </c>
-      <c r="H17" s="2">
         <v>6.25</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="2">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="2">
-        <v>5</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1.0544</v>
-      </c>
       <c r="F18" s="2">
-        <v>17</v>
-      </c>
-      <c r="G18" s="2">
-        <v>17</v>
-      </c>
-      <c r="H18" s="2">
         <v>6.12</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="2">
-        <v>6</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1.0215000000000001</v>
-      </c>
       <c r="F19" s="2">
-        <v>18</v>
-      </c>
-      <c r="G19" s="2">
-        <v>18</v>
-      </c>
-      <c r="H19" s="2">
         <v>6.08</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>47</v>
+      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2">
+        <v>19</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="2">
-        <v>1.1052</v>
+      <c r="E20" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="F20" s="2">
-        <v>19</v>
-      </c>
-      <c r="G20" s="2">
-        <v>19</v>
-      </c>
-      <c r="H20" s="2">
         <v>6.1</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>47</v>
+      <c r="B21" s="2">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2">
+        <v>26</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
       </c>
-      <c r="E21" s="2">
-        <v>1.0369999999999999</v>
+      <c r="E21" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="F21" s="2">
-        <v>20</v>
-      </c>
-      <c r="G21" s="2">
-        <v>26</v>
-      </c>
-      <c r="H21" s="2">
         <v>6.17</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J21" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
+      <c r="B22" s="2">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2">
+        <v>21</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
       </c>
-      <c r="E22" s="2">
-        <v>1.0192000000000001</v>
+      <c r="E22" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="F22" s="2">
-        <v>21</v>
-      </c>
-      <c r="G22" s="2">
-        <v>21</v>
-      </c>
-      <c r="H22" s="2">
         <v>6.16</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="2">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2">
+        <v>22</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
       <c r="F23" s="2">
-        <v>22</v>
-      </c>
-      <c r="G23" s="2">
-        <v>22</v>
-      </c>
-      <c r="H23" s="2">
         <v>6.58</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="2">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2">
+        <v>24</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2</v>
-      </c>
       <c r="F24" s="2">
-        <v>23</v>
-      </c>
-      <c r="G24" s="2">
-        <v>24</v>
-      </c>
-      <c r="H24" s="2">
         <v>6.84</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="2">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2">
+        <v>23</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="2">
-        <v>3</v>
-      </c>
       <c r="F25" s="2">
-        <v>24</v>
-      </c>
-      <c r="G25" s="2">
-        <v>23</v>
-      </c>
-      <c r="H25" s="2">
         <v>6.53</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="2">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data_ankom/metadata.xlsx
+++ b/data_ankom/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arlan\Desktop\rumenGP\data_ankom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D542F273-DFA6-4CC6-B3BD-9E5EF51EC7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF6E642-2244-4F37-AD9F-180EF4189EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{13B5C980-F356-944D-8F6C-78B1F36B7411}"/>
   </bookViews>

--- a/data_ankom/metadata.xlsx
+++ b/data_ankom/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arlan\Desktop\rumenGP\data_ankom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF6E642-2244-4F37-AD9F-180EF4189EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120EA076-F958-43B3-ADFF-EE17D90357A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{13B5C980-F356-944D-8F6C-78B1F36B7411}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -1938,36 +1938,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD47E061-5D39-4811-B47A-D9F9D6DB42BE}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="10.875" style="2"/>
-    <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="10.875" style="2"/>
+    <col min="1" max="2" width="10.875" style="2"/>
+    <col min="3" max="3" width="9.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1977,17 +1974,14 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="2">
+      <c r="E2" s="2">
         <v>6.24</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1997,17 +1991,14 @@
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="2">
+      <c r="E3" s="2">
         <v>6.22</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2017,17 +2008,14 @@
       <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="2">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="2">
+      <c r="E4" s="2">
         <v>6.24</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2035,19 +2023,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="2">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="2">
+      <c r="E5" s="2">
         <v>6.3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2055,19 +2040,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="2">
+      <c r="E6" s="2">
         <v>6.15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2075,19 +2057,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="2">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="2">
+      <c r="E7" s="2">
         <v>6.16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2095,19 +2074,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="2">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="2">
+      <c r="E8" s="2">
         <v>6.13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2115,19 +2091,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="2">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="2">
+      <c r="E9" s="2">
         <v>6.12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2135,19 +2108,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="2">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="2">
+      <c r="E10" s="2">
         <v>6.12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2155,19 +2125,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="2">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="2">
+      <c r="E11" s="2">
         <v>6.26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2175,19 +2142,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="2">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2</v>
-      </c>
-      <c r="E12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="2">
+      <c r="E12" s="2">
         <v>6.12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2195,19 +2159,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="2">
+      <c r="E13" s="2">
         <v>6.17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2215,19 +2176,16 @@
         <v>13</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="2">
+      <c r="E14" s="2">
         <v>6.15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2235,19 +2193,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="2">
-        <v>14</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="2">
+      <c r="E15" s="2">
         <v>6.17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2255,19 +2210,16 @@
         <v>15</v>
       </c>
       <c r="C16" s="2">
-        <v>15</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="2">
+      <c r="E16" s="2">
         <v>6.12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2275,19 +2227,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="2">
-        <v>16</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="2">
+      <c r="E17" s="2">
         <v>6.25</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2295,19 +2244,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
-      </c>
-      <c r="D18" s="2">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="2">
+      <c r="E18" s="2">
         <v>6.12</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2315,19 +2261,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="2">
-        <v>18</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="2">
+      <c r="E19" s="2">
         <v>6.08</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2335,39 +2278,33 @@
         <v>19</v>
       </c>
       <c r="C20" s="2">
-        <v>19</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="2">
+      <c r="E20" s="2">
         <v>6.1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C21" s="2">
-        <v>26</v>
-      </c>
-      <c r="D21" s="2">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="2">
+      <c r="E21" s="2">
         <v>6.17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2375,19 +2312,16 @@
         <v>21</v>
       </c>
       <c r="C22" s="2">
-        <v>21</v>
-      </c>
-      <c r="D22" s="2">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="2">
+      <c r="E22" s="2">
         <v>6.16</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2395,55 +2329,46 @@
         <v>22</v>
       </c>
       <c r="C23" s="2">
-        <v>22</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="2">
+      <c r="E23" s="2">
         <v>6.58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="2">
-        <v>24</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="2">
+      <c r="E24" s="2">
         <v>6.84</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2">
-        <v>23</v>
-      </c>
-      <c r="D25" s="2">
-        <v>3</v>
-      </c>
-      <c r="E25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="2">
+      <c r="E25" s="2">
         <v>6.53</v>
       </c>
     </row>

--- a/data_ankom/metadata.xlsx
+++ b/data_ankom/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arlan\Desktop\rumenGP\data_ankom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A501A401-D5A7-49C0-B27B-D1E1253BAD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CF1AB0-BFA3-444F-BF7D-31D973ABE820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{13B5C980-F356-944D-8F6C-78B1F36B7411}"/>
   </bookViews>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="13">
   <si>
-    <t>Sample</t>
-  </si>
-  <si>
     <t>Bottle</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>R126_1_3</t>
+  </si>
+  <si>
+    <t>Treatment</t>
   </si>
 </sst>
 </file>
@@ -480,19 +480,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -506,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2">
         <v>6.24</v>
@@ -523,7 +523,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2">
         <v>6.22</v>
@@ -540,7 +540,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2">
         <v>6.24</v>
@@ -557,7 +557,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2">
         <v>6.3</v>
@@ -574,7 +574,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2">
         <v>6.15</v>
@@ -591,7 +591,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2">
         <v>6.16</v>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2">
         <v>6.13</v>
@@ -625,7 +625,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2">
         <v>6.12</v>
@@ -642,7 +642,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2">
         <v>6.12</v>
@@ -659,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2">
         <v>6.26</v>
@@ -676,7 +676,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2">
         <v>6.12</v>
@@ -693,7 +693,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2">
         <v>6.17</v>
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2">
         <v>6.15</v>
@@ -727,7 +727,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2">
         <v>6.17</v>
@@ -744,7 +744,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2">
         <v>6.12</v>
@@ -761,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2">
         <v>6.25</v>
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2">
         <v>6.12</v>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2">
         <v>6.08</v>
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2">
         <v>6.1</v>
@@ -829,7 +829,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2">
         <v>6.17</v>
@@ -846,7 +846,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2">
         <v>6.16</v>
@@ -863,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
         <v>6.58</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2">
         <v>6.84</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2">
         <v>6.53</v>
